--- a/experimental/attention/quant_sparse_lightning_indexer_dsl/pytest/excel/qsli_decode_prefill_20cases.xlsx
+++ b/experimental/attention/quant_sparse_lightning_indexer_dsl/pytest/excel/qsli_decode_prefill_20cases.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TestCases" sheetId="1" r:id="Rf131e8efca224ca6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TestCases" sheetId="1" r:id="R62791d978c024404"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -545,9 +545,7 @@
       <x:c r="E2" s="4" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F2" s="4" t="n">
-        <x:v>2048</x:v>
-      </x:c>
+      <x:c r="F2" s="4"/>
       <x:c r="G2" s="4" t="n">
         <x:v>32</x:v>
       </x:c>
@@ -587,7 +585,9 @@
       <x:c r="S2" s="4" t="str">
         <x:v>[2041]</x:v>
       </x:c>
-      <x:c r="T2" s="4"/>
+      <x:c r="T2" s="4" t="str">
+        <x:v>[0]</x:v>
+      </x:c>
       <x:c r="U2" s="4" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -622,19 +622,19 @@
         <x:v>[1,65504]</x:v>
       </x:c>
       <x:c r="AF2" s="4" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AG2" s="5" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AH2" s="5" t="b">
-        <x:v>1</x:v>
+      <x:c r="AH2" s="4" t="str">
+        <x:v>AUTO</x:v>
       </x:c>
       <x:c r="AI2" s="4" t="str">
         <x:v>AUTO</x:v>
       </x:c>
-      <x:c r="AJ2" s="4" t="n">
-        <x:v>64</x:v>
+      <x:c r="AJ2" s="4" t="str">
+        <x:v>AUTO</x:v>
       </x:c>
       <x:c r="AK2" s="4" t="n">
         <x:v>8</x:v>
@@ -665,9 +665,7 @@
       <x:c r="E3" s="4" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F3" s="4" t="n">
-        <x:v>4096</x:v>
-      </x:c>
+      <x:c r="F3" s="4"/>
       <x:c r="G3" s="4" t="n">
         <x:v>32</x:v>
       </x:c>
@@ -707,7 +705,9 @@
       <x:c r="S3" s="4" t="str">
         <x:v>[4089,4058,4027,3996]</x:v>
       </x:c>
-      <x:c r="T3" s="4"/>
+      <x:c r="T3" s="4" t="str">
+        <x:v>[0,1,0,1]</x:v>
+      </x:c>
       <x:c r="U3" s="4" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -742,19 +742,19 @@
         <x:v>[1,65504]</x:v>
       </x:c>
       <x:c r="AF3" s="4" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AG3" s="5" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AH3" s="5" t="b">
-        <x:v>1</x:v>
+      <x:c r="AH3" s="4" t="str">
+        <x:v>AUTO</x:v>
       </x:c>
       <x:c r="AI3" s="4" t="str">
         <x:v>AUTO</x:v>
       </x:c>
-      <x:c r="AJ3" s="4" t="n">
-        <x:v>64</x:v>
+      <x:c r="AJ3" s="4" t="str">
+        <x:v>AUTO</x:v>
       </x:c>
       <x:c r="AK3" s="4" t="n">
         <x:v>8</x:v>
@@ -785,9 +785,7 @@
       <x:c r="E4" s="4" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="F4" s="4" t="n">
-        <x:v>8192</x:v>
-      </x:c>
+      <x:c r="F4" s="4"/>
       <x:c r="G4" s="4" t="n">
         <x:v>32</x:v>
       </x:c>
@@ -827,7 +825,9 @@
       <x:c r="S4" s="4" t="str">
         <x:v>[8185,8154,8123,8092,8189,8158,8127,8096]</x:v>
       </x:c>
-      <x:c r="T4" s="4"/>
+      <x:c r="T4" s="4" t="str">
+        <x:v>[0,1,0,1,0,1,0,1]</x:v>
+      </x:c>
       <x:c r="U4" s="4" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -862,19 +862,19 @@
         <x:v>[1,65504]</x:v>
       </x:c>
       <x:c r="AF4" s="4" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AG4" s="5" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AH4" s="5" t="b">
-        <x:v>1</x:v>
+      <x:c r="AH4" s="4" t="str">
+        <x:v>AUTO</x:v>
       </x:c>
       <x:c r="AI4" s="4" t="str">
         <x:v>AUTO</x:v>
       </x:c>
-      <x:c r="AJ4" s="4" t="n">
-        <x:v>64</x:v>
+      <x:c r="AJ4" s="4" t="str">
+        <x:v>AUTO</x:v>
       </x:c>
       <x:c r="AK4" s="4" t="n">
         <x:v>8</x:v>
@@ -905,9 +905,7 @@
       <x:c r="E5" s="4" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F5" s="4" t="n">
-        <x:v>16384</x:v>
-      </x:c>
+      <x:c r="F5" s="4"/>
       <x:c r="G5" s="4" t="n">
         <x:v>32</x:v>
       </x:c>
@@ -947,7 +945,9 @@
       <x:c r="S5" s="4" t="str">
         <x:v>[16377,16346,16315,16284,16381,16350,16319,16288,16257,16354,16323,16292,16261,16358,16327,16296]</x:v>
       </x:c>
-      <x:c r="T5" s="4"/>
+      <x:c r="T5" s="4" t="str">
+        <x:v>[0,1,0,1,0,1,0,1,0,1,0,1,0,1,0,1]</x:v>
+      </x:c>
       <x:c r="U5" s="4" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -982,19 +982,19 @@
         <x:v>[1,65504]</x:v>
       </x:c>
       <x:c r="AF5" s="4" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AG5" s="5" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AH5" s="5" t="b">
-        <x:v>1</x:v>
+      <x:c r="AH5" s="4" t="str">
+        <x:v>AUTO</x:v>
       </x:c>
       <x:c r="AI5" s="4" t="str">
         <x:v>AUTO</x:v>
       </x:c>
-      <x:c r="AJ5" s="4" t="n">
-        <x:v>64</x:v>
+      <x:c r="AJ5" s="4" t="str">
+        <x:v>AUTO</x:v>
       </x:c>
       <x:c r="AK5" s="4" t="n">
         <x:v>8</x:v>
@@ -1025,9 +1025,7 @@
       <x:c r="E6" s="4" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="F6" s="4" t="n">
-        <x:v>32768</x:v>
-      </x:c>
+      <x:c r="F6" s="4"/>
       <x:c r="G6" s="4" t="n">
         <x:v>32</x:v>
       </x:c>
@@ -1067,7 +1065,9 @@
       <x:c r="S6" s="4" t="str">
         <x:v>[32761,32730,32699,32668,32765,32734,32703,32672,32641,32738,32707,32676,32645,32742,32711,32680,32649,32746,32715,32684,32653,32750,32719,32688,32657,32754,32723,32692,32661,32758,32727,32696]</x:v>
       </x:c>
-      <x:c r="T6" s="4"/>
+      <x:c r="T6" s="4" t="str">
+        <x:v>[0,1,0,1,0,1,0,1,0,1,0,1,0,1,0,1,0,1,0,1,0,1,0,1,0,1,0,1,0,1,0,1]</x:v>
+      </x:c>
       <x:c r="U6" s="4" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -1102,19 +1102,19 @@
         <x:v>[1,65504]</x:v>
       </x:c>
       <x:c r="AF6" s="4" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AG6" s="5" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AH6" s="5" t="b">
-        <x:v>1</x:v>
+      <x:c r="AH6" s="4" t="str">
+        <x:v>AUTO</x:v>
       </x:c>
       <x:c r="AI6" s="4" t="str">
         <x:v>AUTO</x:v>
       </x:c>
-      <x:c r="AJ6" s="4" t="n">
-        <x:v>64</x:v>
+      <x:c r="AJ6" s="4" t="str">
+        <x:v>AUTO</x:v>
       </x:c>
       <x:c r="AK6" s="4" t="n">
         <x:v>8</x:v>
@@ -1145,9 +1145,7 @@
       <x:c r="E7" s="4" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="4" t="n">
-        <x:v>2048</x:v>
-      </x:c>
+      <x:c r="F7" s="4"/>
       <x:c r="G7" s="4" t="n">
         <x:v>32</x:v>
       </x:c>
@@ -1187,7 +1185,9 @@
       <x:c r="S7" s="4" t="str">
         <x:v>[2020]</x:v>
       </x:c>
-      <x:c r="T7" s="4"/>
+      <x:c r="T7" s="4" t="str">
+        <x:v>[0]</x:v>
+      </x:c>
       <x:c r="U7" s="4" t="n">
         <x:v>4</x:v>
       </x:c>
@@ -1222,19 +1222,19 @@
         <x:v>[1,65504]</x:v>
       </x:c>
       <x:c r="AF7" s="4" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AG7" s="5" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AH7" s="5" t="b">
-        <x:v>1</x:v>
+      <x:c r="AH7" s="4" t="str">
+        <x:v>AUTO</x:v>
       </x:c>
       <x:c r="AI7" s="4" t="str">
         <x:v>AUTO</x:v>
       </x:c>
-      <x:c r="AJ7" s="4" t="n">
-        <x:v>64</x:v>
+      <x:c r="AJ7" s="4" t="str">
+        <x:v>AUTO</x:v>
       </x:c>
       <x:c r="AK7" s="4" t="n">
         <x:v>8</x:v>
@@ -1265,9 +1265,7 @@
       <x:c r="E8" s="4" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F8" s="4" t="n">
-        <x:v>4096</x:v>
-      </x:c>
+      <x:c r="F8" s="4"/>
       <x:c r="G8" s="4" t="n">
         <x:v>32</x:v>
       </x:c>
@@ -1307,7 +1305,9 @@
       <x:c r="S8" s="4" t="str">
         <x:v>[4068,4037,4006,3975]</x:v>
       </x:c>
-      <x:c r="T8" s="4"/>
+      <x:c r="T8" s="4" t="str">
+        <x:v>[0,1,0,1]</x:v>
+      </x:c>
       <x:c r="U8" s="4" t="n">
         <x:v>4</x:v>
       </x:c>
@@ -1342,19 +1342,19 @@
         <x:v>[1,65504]</x:v>
       </x:c>
       <x:c r="AF8" s="4" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AG8" s="5" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AH8" s="5" t="b">
-        <x:v>1</x:v>
+      <x:c r="AH8" s="4" t="str">
+        <x:v>AUTO</x:v>
       </x:c>
       <x:c r="AI8" s="4" t="str">
         <x:v>AUTO</x:v>
       </x:c>
-      <x:c r="AJ8" s="4" t="n">
-        <x:v>64</x:v>
+      <x:c r="AJ8" s="4" t="str">
+        <x:v>AUTO</x:v>
       </x:c>
       <x:c r="AK8" s="4" t="n">
         <x:v>8</x:v>
@@ -1385,9 +1385,7 @@
       <x:c r="E9" s="4" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="F9" s="4" t="n">
-        <x:v>8192</x:v>
-      </x:c>
+      <x:c r="F9" s="4"/>
       <x:c r="G9" s="4" t="n">
         <x:v>32</x:v>
       </x:c>
@@ -1427,7 +1425,9 @@
       <x:c r="S9" s="4" t="str">
         <x:v>[8164,8133,8102,8071,8168,8137,8106,8075]</x:v>
       </x:c>
-      <x:c r="T9" s="4"/>
+      <x:c r="T9" s="4" t="str">
+        <x:v>[0,1,0,1,0,1,0,1]</x:v>
+      </x:c>
       <x:c r="U9" s="4" t="n">
         <x:v>4</x:v>
       </x:c>
@@ -1462,19 +1462,19 @@
         <x:v>[1,65504]</x:v>
       </x:c>
       <x:c r="AF9" s="4" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AG9" s="5" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AH9" s="5" t="b">
-        <x:v>1</x:v>
+      <x:c r="AH9" s="4" t="str">
+        <x:v>AUTO</x:v>
       </x:c>
       <x:c r="AI9" s="4" t="str">
         <x:v>AUTO</x:v>
       </x:c>
-      <x:c r="AJ9" s="4" t="n">
-        <x:v>64</x:v>
+      <x:c r="AJ9" s="4" t="str">
+        <x:v>AUTO</x:v>
       </x:c>
       <x:c r="AK9" s="4" t="n">
         <x:v>8</x:v>
@@ -1505,9 +1505,7 @@
       <x:c r="E10" s="4" t="n">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="F10" s="4" t="n">
-        <x:v>16384</x:v>
-      </x:c>
+      <x:c r="F10" s="4"/>
       <x:c r="G10" s="4" t="n">
         <x:v>32</x:v>
       </x:c>
@@ -1547,7 +1545,9 @@
       <x:c r="S10" s="4" t="str">
         <x:v>[16356,16325,16294,16263,16360,16329,16298,16267,16364,16333,16302,16271,16368,16337,16306,16275]</x:v>
       </x:c>
-      <x:c r="T10" s="4"/>
+      <x:c r="T10" s="4" t="str">
+        <x:v>[0,1,0,1,0,1,0,1,0,1,0,1,0,1,0,1]</x:v>
+      </x:c>
       <x:c r="U10" s="4" t="n">
         <x:v>4</x:v>
       </x:c>
@@ -1582,19 +1582,19 @@
         <x:v>[1,65504]</x:v>
       </x:c>
       <x:c r="AF10" s="4" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AG10" s="5" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AH10" s="5" t="b">
-        <x:v>1</x:v>
+      <x:c r="AH10" s="4" t="str">
+        <x:v>AUTO</x:v>
       </x:c>
       <x:c r="AI10" s="4" t="str">
         <x:v>AUTO</x:v>
       </x:c>
-      <x:c r="AJ10" s="4" t="n">
-        <x:v>64</x:v>
+      <x:c r="AJ10" s="4" t="str">
+        <x:v>AUTO</x:v>
       </x:c>
       <x:c r="AK10" s="4" t="n">
         <x:v>8</x:v>
@@ -1625,9 +1625,7 @@
       <x:c r="E11" s="4" t="n">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="F11" s="4" t="n">
-        <x:v>32768</x:v>
-      </x:c>
+      <x:c r="F11" s="4"/>
       <x:c r="G11" s="4" t="n">
         <x:v>32</x:v>
       </x:c>
@@ -1667,7 +1665,9 @@
       <x:c r="S11" s="4" t="str">
         <x:v>[32740,32709,32678,32647,32744,32713,32682,32651,32748,32717,32686,32655,32752,32721,32690,32659,32756,32725,32694,32663,32760,32729,32698,32667,32764,32733,32702,32671,32768,32737,32706,32675]</x:v>
       </x:c>
-      <x:c r="T11" s="4"/>
+      <x:c r="T11" s="4" t="str">
+        <x:v>[0,1,0,1,0,1,0,1,0,1,0,1,0,1,0,1,0,1,0,1,0,1,0,1,0,1,0,1,0,1,0,1]</x:v>
+      </x:c>
       <x:c r="U11" s="4" t="n">
         <x:v>4</x:v>
       </x:c>
@@ -1702,19 +1702,19 @@
         <x:v>[1,65504]</x:v>
       </x:c>
       <x:c r="AF11" s="4" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AG11" s="5" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AH11" s="5" t="b">
-        <x:v>1</x:v>
+      <x:c r="AH11" s="4" t="str">
+        <x:v>AUTO</x:v>
       </x:c>
       <x:c r="AI11" s="4" t="str">
         <x:v>AUTO</x:v>
       </x:c>
-      <x:c r="AJ11" s="4" t="n">
-        <x:v>64</x:v>
+      <x:c r="AJ11" s="4" t="str">
+        <x:v>AUTO</x:v>
       </x:c>
       <x:c r="AK11" s="4" t="n">
         <x:v>8</x:v>
@@ -1745,9 +1745,7 @@
       <x:c r="E12" s="4" t="n">
         <x:v>8192</x:v>
       </x:c>
-      <x:c r="F12" s="4" t="n">
-        <x:v>2048</x:v>
-      </x:c>
+      <x:c r="F12" s="4"/>
       <x:c r="G12" s="4" t="n">
         <x:v>32</x:v>
       </x:c>
@@ -1787,7 +1785,9 @@
       <x:c r="S12" s="4" t="str">
         <x:v>[2048]</x:v>
       </x:c>
-      <x:c r="T12" s="4"/>
+      <x:c r="T12" s="4" t="str">
+        <x:v>[0]</x:v>
+      </x:c>
       <x:c r="U12" s="4" t="n">
         <x:v>8192</x:v>
       </x:c>
@@ -1804,7 +1804,7 @@
         <x:v>512</x:v>
       </x:c>
       <x:c r="Z12" s="4" t="n">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AA12" s="4" t="str">
         <x:v>[-6,6]</x:v>
@@ -1822,19 +1822,19 @@
         <x:v>[1,65504]</x:v>
       </x:c>
       <x:c r="AF12" s="4" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AG12" s="5" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AH12" s="5" t="b">
-        <x:v>1</x:v>
+      <x:c r="AH12" s="4" t="str">
+        <x:v>AUTO</x:v>
       </x:c>
       <x:c r="AI12" s="4" t="str">
         <x:v>AUTO</x:v>
       </x:c>
-      <x:c r="AJ12" s="4" t="n">
-        <x:v>64</x:v>
+      <x:c r="AJ12" s="4" t="str">
+        <x:v>AUTO</x:v>
       </x:c>
       <x:c r="AK12" s="4" t="n">
         <x:v>8</x:v>
@@ -1865,9 +1865,7 @@
       <x:c r="E13" s="4" t="n">
         <x:v>8195</x:v>
       </x:c>
-      <x:c r="F13" s="4" t="n">
-        <x:v>4096</x:v>
-      </x:c>
+      <x:c r="F13" s="4"/>
       <x:c r="G13" s="4" t="n">
         <x:v>32</x:v>
       </x:c>
@@ -1907,7 +1905,9 @@
       <x:c r="S13" s="4" t="str">
         <x:v>[4096,4079,4062,4045]</x:v>
       </x:c>
-      <x:c r="T13" s="4"/>
+      <x:c r="T13" s="4" t="str">
+        <x:v>[0,1,0,1]</x:v>
+      </x:c>
       <x:c r="U13" s="4" t="n">
         <x:v>8192</x:v>
       </x:c>
@@ -1924,7 +1924,7 @@
         <x:v>512</x:v>
       </x:c>
       <x:c r="Z13" s="4" t="n">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AA13" s="4" t="str">
         <x:v>[-6,6]</x:v>
@@ -1942,19 +1942,19 @@
         <x:v>[1,65504]</x:v>
       </x:c>
       <x:c r="AF13" s="4" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AG13" s="5" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AH13" s="5" t="b">
-        <x:v>1</x:v>
+      <x:c r="AH13" s="4" t="str">
+        <x:v>AUTO</x:v>
       </x:c>
       <x:c r="AI13" s="4" t="str">
         <x:v>AUTO</x:v>
       </x:c>
-      <x:c r="AJ13" s="4" t="n">
-        <x:v>64</x:v>
+      <x:c r="AJ13" s="4" t="str">
+        <x:v>AUTO</x:v>
       </x:c>
       <x:c r="AK13" s="4" t="n">
         <x:v>8</x:v>
@@ -1985,9 +1985,7 @@
       <x:c r="E14" s="4" t="n">
         <x:v>8199</x:v>
       </x:c>
-      <x:c r="F14" s="4" t="n">
-        <x:v>8192</x:v>
-      </x:c>
+      <x:c r="F14" s="4"/>
       <x:c r="G14" s="4" t="n">
         <x:v>32</x:v>
       </x:c>
@@ -2027,7 +2025,9 @@
       <x:c r="S14" s="4" t="str">
         <x:v>[8192,8175,8158,8141,8124,8107,8090,8073]</x:v>
       </x:c>
-      <x:c r="T14" s="4"/>
+      <x:c r="T14" s="4" t="str">
+        <x:v>[0,1,0,1,0,1,0,1]</x:v>
+      </x:c>
       <x:c r="U14" s="4" t="n">
         <x:v>8192</x:v>
       </x:c>
@@ -2044,7 +2044,7 @@
         <x:v>512</x:v>
       </x:c>
       <x:c r="Z14" s="4" t="n">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AA14" s="4" t="str">
         <x:v>[-6,6]</x:v>
@@ -2062,19 +2062,19 @@
         <x:v>[1,65504]</x:v>
       </x:c>
       <x:c r="AF14" s="4" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AG14" s="5" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AH14" s="5" t="b">
-        <x:v>1</x:v>
+      <x:c r="AH14" s="4" t="str">
+        <x:v>AUTO</x:v>
       </x:c>
       <x:c r="AI14" s="4" t="str">
         <x:v>AUTO</x:v>
       </x:c>
-      <x:c r="AJ14" s="4" t="n">
-        <x:v>64</x:v>
+      <x:c r="AJ14" s="4" t="str">
+        <x:v>AUTO</x:v>
       </x:c>
       <x:c r="AK14" s="4" t="n">
         <x:v>8</x:v>
@@ -2105,9 +2105,7 @@
       <x:c r="E15" s="4" t="n">
         <x:v>8207</x:v>
       </x:c>
-      <x:c r="F15" s="4" t="n">
-        <x:v>16384</x:v>
-      </x:c>
+      <x:c r="F15" s="4"/>
       <x:c r="G15" s="4" t="n">
         <x:v>32</x:v>
       </x:c>
@@ -2147,7 +2145,9 @@
       <x:c r="S15" s="4" t="str">
         <x:v>[16384,16367,16350,16333,16316,16299,16282,16265,16376,16359,16342,16325,16308,16291,16274,16257]</x:v>
       </x:c>
-      <x:c r="T15" s="4"/>
+      <x:c r="T15" s="4" t="str">
+        <x:v>[0,1,0,1,0,1,0,1,0,1,0,1,0,1,0,1]</x:v>
+      </x:c>
       <x:c r="U15" s="4" t="n">
         <x:v>8192</x:v>
       </x:c>
@@ -2164,7 +2164,7 @@
         <x:v>512</x:v>
       </x:c>
       <x:c r="Z15" s="4" t="n">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AA15" s="4" t="str">
         <x:v>[-6,6]</x:v>
@@ -2182,19 +2182,19 @@
         <x:v>[1,65504]</x:v>
       </x:c>
       <x:c r="AF15" s="4" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AG15" s="5" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AH15" s="5" t="b">
-        <x:v>1</x:v>
+      <x:c r="AH15" s="4" t="str">
+        <x:v>AUTO</x:v>
       </x:c>
       <x:c r="AI15" s="4" t="str">
         <x:v>AUTO</x:v>
       </x:c>
-      <x:c r="AJ15" s="4" t="n">
-        <x:v>64</x:v>
+      <x:c r="AJ15" s="4" t="str">
+        <x:v>AUTO</x:v>
       </x:c>
       <x:c r="AK15" s="4" t="n">
         <x:v>8</x:v>
@@ -2225,9 +2225,7 @@
       <x:c r="E16" s="4" t="n">
         <x:v>8223</x:v>
       </x:c>
-      <x:c r="F16" s="4" t="n">
-        <x:v>32768</x:v>
-      </x:c>
+      <x:c r="F16" s="4"/>
       <x:c r="G16" s="4" t="n">
         <x:v>32</x:v>
       </x:c>
@@ -2267,7 +2265,9 @@
       <x:c r="S16" s="4" t="str">
         <x:v>[32768,32751,32734,32717,32700,32683,32666,32649,32760,32743,32726,32709,32692,32675,32658,32641,32752,32735,32718,32701,32684,32667,32650,32761,32744,32727,32710,32693,32676,32659,32642,32753]</x:v>
       </x:c>
-      <x:c r="T16" s="4"/>
+      <x:c r="T16" s="4" t="str">
+        <x:v>[0,1,0,1,0,1,0,1,0,1,0,1,0,1,0,1,0,1,0,1,0,1,0,1,0,1,0,1,0,1,0,1]</x:v>
+      </x:c>
       <x:c r="U16" s="4" t="n">
         <x:v>8192</x:v>
       </x:c>
@@ -2284,7 +2284,7 @@
         <x:v>512</x:v>
       </x:c>
       <x:c r="Z16" s="4" t="n">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AA16" s="4" t="str">
         <x:v>[-6,6]</x:v>
@@ -2302,19 +2302,19 @@
         <x:v>[1,65504]</x:v>
       </x:c>
       <x:c r="AF16" s="4" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AG16" s="5" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AH16" s="5" t="b">
-        <x:v>1</x:v>
+      <x:c r="AH16" s="4" t="str">
+        <x:v>AUTO</x:v>
       </x:c>
       <x:c r="AI16" s="4" t="str">
         <x:v>AUTO</x:v>
       </x:c>
-      <x:c r="AJ16" s="4" t="n">
-        <x:v>64</x:v>
+      <x:c r="AJ16" s="4" t="str">
+        <x:v>AUTO</x:v>
       </x:c>
       <x:c r="AK16" s="4" t="n">
         <x:v>8</x:v>
@@ -2345,9 +2345,7 @@
       <x:c r="E17" s="4" t="n">
         <x:v>8192</x:v>
       </x:c>
-      <x:c r="F17" s="4" t="n">
-        <x:v>2048</x:v>
-      </x:c>
+      <x:c r="F17" s="4"/>
       <x:c r="G17" s="4" t="n">
         <x:v>32</x:v>
       </x:c>
@@ -2387,7 +2385,9 @@
       <x:c r="S17" s="4" t="str">
         <x:v>[1921]</x:v>
       </x:c>
-      <x:c r="T17" s="4"/>
+      <x:c r="T17" s="4" t="str">
+        <x:v>[0]</x:v>
+      </x:c>
       <x:c r="U17" s="4" t="n">
         <x:v>8192</x:v>
       </x:c>
@@ -2404,7 +2404,7 @@
         <x:v>512</x:v>
       </x:c>
       <x:c r="Z17" s="4" t="n">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AA17" s="4" t="str">
         <x:v>[-6,6]</x:v>
@@ -2422,19 +2422,19 @@
         <x:v>[1,65504]</x:v>
       </x:c>
       <x:c r="AF17" s="4" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AG17" s="5" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AH17" s="5" t="b">
-        <x:v>1</x:v>
+      <x:c r="AH17" s="4" t="str">
+        <x:v>AUTO</x:v>
       </x:c>
       <x:c r="AI17" s="4" t="str">
         <x:v>AUTO</x:v>
       </x:c>
-      <x:c r="AJ17" s="4" t="n">
-        <x:v>64</x:v>
+      <x:c r="AJ17" s="4" t="str">
+        <x:v>AUTO</x:v>
       </x:c>
       <x:c r="AK17" s="4" t="n">
         <x:v>8</x:v>
@@ -2465,9 +2465,7 @@
       <x:c r="E18" s="4" t="n">
         <x:v>8204</x:v>
       </x:c>
-      <x:c r="F18" s="4" t="n">
-        <x:v>4096</x:v>
-      </x:c>
+      <x:c r="F18" s="4"/>
       <x:c r="G18" s="4" t="n">
         <x:v>32</x:v>
       </x:c>
@@ -2507,7 +2505,9 @@
       <x:c r="S18" s="4" t="str">
         <x:v>[3969,3938,3907,3876]</x:v>
       </x:c>
-      <x:c r="T18" s="4"/>
+      <x:c r="T18" s="4" t="str">
+        <x:v>[0,1,0,1]</x:v>
+      </x:c>
       <x:c r="U18" s="4" t="n">
         <x:v>8192</x:v>
       </x:c>
@@ -2524,7 +2524,7 @@
         <x:v>512</x:v>
       </x:c>
       <x:c r="Z18" s="4" t="n">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AA18" s="4" t="str">
         <x:v>[-6,6]</x:v>
@@ -2542,19 +2542,19 @@
         <x:v>[1,65504]</x:v>
       </x:c>
       <x:c r="AF18" s="4" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AG18" s="5" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AH18" s="5" t="b">
-        <x:v>1</x:v>
+      <x:c r="AH18" s="4" t="str">
+        <x:v>AUTO</x:v>
       </x:c>
       <x:c r="AI18" s="4" t="str">
         <x:v>AUTO</x:v>
       </x:c>
-      <x:c r="AJ18" s="4" t="n">
-        <x:v>64</x:v>
+      <x:c r="AJ18" s="4" t="str">
+        <x:v>AUTO</x:v>
       </x:c>
       <x:c r="AK18" s="4" t="n">
         <x:v>8</x:v>
@@ -2585,9 +2585,7 @@
       <x:c r="E19" s="4" t="n">
         <x:v>8220</x:v>
       </x:c>
-      <x:c r="F19" s="4" t="n">
-        <x:v>8192</x:v>
-      </x:c>
+      <x:c r="F19" s="4"/>
       <x:c r="G19" s="4" t="n">
         <x:v>32</x:v>
       </x:c>
@@ -2627,7 +2625,9 @@
       <x:c r="S19" s="4" t="str">
         <x:v>[8065,8034,8003,7972,7941,7910,7879,7848]</x:v>
       </x:c>
-      <x:c r="T19" s="4"/>
+      <x:c r="T19" s="4" t="str">
+        <x:v>[0,1,0,1,0,1,0,1]</x:v>
+      </x:c>
       <x:c r="U19" s="4" t="n">
         <x:v>8192</x:v>
       </x:c>
@@ -2644,7 +2644,7 @@
         <x:v>512</x:v>
       </x:c>
       <x:c r="Z19" s="4" t="n">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AA19" s="4" t="str">
         <x:v>[-6,6]</x:v>
@@ -2662,19 +2662,19 @@
         <x:v>[1,65504]</x:v>
       </x:c>
       <x:c r="AF19" s="4" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AG19" s="5" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AH19" s="5" t="b">
-        <x:v>1</x:v>
+      <x:c r="AH19" s="4" t="str">
+        <x:v>AUTO</x:v>
       </x:c>
       <x:c r="AI19" s="4" t="str">
         <x:v>AUTO</x:v>
       </x:c>
-      <x:c r="AJ19" s="4" t="n">
-        <x:v>64</x:v>
+      <x:c r="AJ19" s="4" t="str">
+        <x:v>AUTO</x:v>
       </x:c>
       <x:c r="AK19" s="4" t="n">
         <x:v>8</x:v>
@@ -2705,9 +2705,7 @@
       <x:c r="E20" s="4" t="n">
         <x:v>8252</x:v>
       </x:c>
-      <x:c r="F20" s="4" t="n">
-        <x:v>16384</x:v>
-      </x:c>
+      <x:c r="F20" s="4"/>
       <x:c r="G20" s="4" t="n">
         <x:v>32</x:v>
       </x:c>
@@ -2747,7 +2745,9 @@
       <x:c r="S20" s="4" t="str">
         <x:v>[16257,16226,16195,16164,16133,16102,16071,16040,16009,16234,16203,16172,16141,16110,16079,16048]</x:v>
       </x:c>
-      <x:c r="T20" s="4"/>
+      <x:c r="T20" s="4" t="str">
+        <x:v>[0,1,0,1,0,1,0,1,0,1,0,1,0,1,0,1]</x:v>
+      </x:c>
       <x:c r="U20" s="4" t="n">
         <x:v>8192</x:v>
       </x:c>
@@ -2764,7 +2764,7 @@
         <x:v>512</x:v>
       </x:c>
       <x:c r="Z20" s="4" t="n">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AA20" s="4" t="str">
         <x:v>[-6,6]</x:v>
@@ -2782,19 +2782,19 @@
         <x:v>[1,65504]</x:v>
       </x:c>
       <x:c r="AF20" s="4" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AG20" s="5" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AH20" s="5" t="b">
-        <x:v>1</x:v>
+      <x:c r="AH20" s="4" t="str">
+        <x:v>AUTO</x:v>
       </x:c>
       <x:c r="AI20" s="4" t="str">
         <x:v>AUTO</x:v>
       </x:c>
-      <x:c r="AJ20" s="4" t="n">
-        <x:v>64</x:v>
+      <x:c r="AJ20" s="4" t="str">
+        <x:v>AUTO</x:v>
       </x:c>
       <x:c r="AK20" s="4" t="n">
         <x:v>8</x:v>
@@ -2825,9 +2825,7 @@
       <x:c r="E21" s="4" t="n">
         <x:v>8316</x:v>
       </x:c>
-      <x:c r="F21" s="4" t="n">
-        <x:v>32768</x:v>
-      </x:c>
+      <x:c r="F21" s="4"/>
       <x:c r="G21" s="4" t="n">
         <x:v>32</x:v>
       </x:c>
@@ -2867,7 +2865,9 @@
       <x:c r="S21" s="4" t="str">
         <x:v>[32641,32610,32579,32548,32517,32486,32455,32424,32393,32618,32587,32556,32525,32494,32463,32432,32401,32626,32595,32564,32533,32502,32471,32440,32409,32634,32603,32572,32541,32510,32479,32448]</x:v>
       </x:c>
-      <x:c r="T21" s="4"/>
+      <x:c r="T21" s="4" t="str">
+        <x:v>[0,1,0,1,0,1,0,1,0,1,0,1,0,1,0,1,0,1,0,1,0,1,0,1,0,1,0,1,0,1,0,1]</x:v>
+      </x:c>
       <x:c r="U21" s="4" t="n">
         <x:v>8192</x:v>
       </x:c>
@@ -2884,7 +2884,7 @@
         <x:v>512</x:v>
       </x:c>
       <x:c r="Z21" s="4" t="n">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AA21" s="4" t="str">
         <x:v>[-6,6]</x:v>
@@ -2902,19 +2902,19 @@
         <x:v>[1,65504]</x:v>
       </x:c>
       <x:c r="AF21" s="4" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AG21" s="5" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AH21" s="5" t="b">
-        <x:v>1</x:v>
+      <x:c r="AH21" s="4" t="str">
+        <x:v>AUTO</x:v>
       </x:c>
       <x:c r="AI21" s="4" t="str">
         <x:v>AUTO</x:v>
       </x:c>
-      <x:c r="AJ21" s="4" t="n">
-        <x:v>64</x:v>
+      <x:c r="AJ21" s="4" t="str">
+        <x:v>AUTO</x:v>
       </x:c>
       <x:c r="AK21" s="4" t="n">
         <x:v>8</x:v>
@@ -2932,7 +2932,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1629081c72514106"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe187dda9f4040b8"/>
   </x:tableParts>
 </x:worksheet>
 </file>